--- a/config/excel/CfgBossRewards.xlsx
+++ b/config/excel/CfgBossRewards.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgBossRewards" sheetId="1" r:id="Rb88810b4c5454b65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgBossRewards" sheetId="1" r:id="R01847e35f51249d4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,82 +13,35 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:fonts count="1">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:name val="Microsoft YaHei"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Microsoft YaHei"/>
-    </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Microsoft YaHei"/>
-    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="2">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
     </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF17365D"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFDBEAF7"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF2CC"/>
-      </x:patternFill>
-    </x:fill>
   </x:fills>
   <x:borders count="1">
-    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="11">
+  <x:cellXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
@@ -313,227 +266,179 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
-  </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+    <x:row r="1">
+      <x:c r="A1" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
-        <x:v>Rounds</x:v>
-      </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="B1" t="str">
+        <x:v>ItemCount</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
         <x:v>EquipmentPoolID</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" t="str">
         <x:v>CollectionIDs</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" t="str">
         <x:v>EquipmentWeight</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" t="str">
         <x:v>CollectionWeight</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="G1" t="str">
         <x:v>MinQuality</x:v>
       </x:c>
-      <x:c r="H1" s="5" t="str">
+      <x:c r="H1" t="str">
         <x:v>MaxQuality</x:v>
       </x:c>
-      <x:c r="I1" s="5" t="str">
-        <x:v>MinEquipmentCandidates</x:v>
-      </x:c>
-      <x:c r="J1" s="5" t="str">
-        <x:v>MinCollectionCandidates</x:v>
-      </x:c>
-      <x:c r="K1" s="5" t="str">
+      <x:c r="I1" t="str">
+        <x:v>MinEquipmentItems</x:v>
+      </x:c>
+      <x:c r="J1" t="str">
+        <x:v>MinCollectionItems</x:v>
+      </x:c>
+      <x:c r="K1" t="str">
         <x:v>AllowRepeatCollections</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="6" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="B2" s="6" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="C2" s="6" t="str">
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="str">
+      <x:c r="D2" t="str">
         <x:v>string[]</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="F2" s="6" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="G2" s="6" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="H2" s="6" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="I2" s="6" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="J2" s="6" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="K2" s="6" t="str">
+      <x:c r="E2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="F2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="G2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="H2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="I2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="J2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="K2" t="str">
         <x:v>bool</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="42" customHeight="1">
-      <x:c r="A3" s="8" t="str">
-        <x:v># 奖励规则编号</x:v>
-      </x:c>
-      <x:c r="B3" s="8" t="str">
-        <x:v>连续选择轮数</x:v>
-      </x:c>
-      <x:c r="C3" s="8" t="str">
-        <x:v>装备独立池</x:v>
-      </x:c>
-      <x:c r="D3" s="8" t="str">
-        <x:v>收藏候选定义</x:v>
-      </x:c>
-      <x:c r="E3" s="8" t="str">
-        <x:v>装备类别权重</x:v>
-      </x:c>
-      <x:c r="F3" s="8" t="str">
-        <x:v>收藏类别权重</x:v>
-      </x:c>
-      <x:c r="G3" s="8" t="str">
-        <x:v>装备最低品质</x:v>
-      </x:c>
-      <x:c r="H3" s="8" t="str">
-        <x:v>装备最高品质</x:v>
-      </x:c>
-      <x:c r="I3" s="8" t="str">
-        <x:v>每轮至少装备数</x:v>
-      </x:c>
-      <x:c r="J3" s="8" t="str">
-        <x:v>每轮至少收藏数</x:v>
-      </x:c>
-      <x:c r="K3" s="8" t="str">
-        <x:v>跨轮允许重复收藏</x:v>
+    <x:row r="3">
+      <x:c r="A3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>boss_equipment</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>gate_sigil</x:v>
+      </x:c>
+      <x:c r="E3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H3" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K3" s="1" t="b">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B4" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="9" t="str">
+    <x:row r="4">
+      <x:c r="A4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
         <x:v>boss_equipment</x:v>
       </x:c>
-      <x:c r="D4" s="9" t="str">
-        <x:v>gate_sigil</x:v>
-      </x:c>
-      <x:c r="E4" s="9" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F4" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G4" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="9" t="n">
+      <x:c r="D4" t="str">
+        <x:v>court_medal</x:v>
+      </x:c>
+      <x:c r="E4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H4" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I4" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J4" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K4" s="10" t="b">
+      <x:c r="I4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K4" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="24" customHeight="1">
-      <x:c r="A5" s="9" t="n">
+    <x:row r="5">
+      <x:c r="A5" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B5" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>boss_equipment</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>core_fragment,gate_sigil,court_medal</x:v>
+      </x:c>
+      <x:c r="E5" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F5" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B5" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="9" t="str">
-        <x:v>boss_equipment</x:v>
-      </x:c>
-      <x:c r="D5" s="9" t="str">
-        <x:v>court_medal</x:v>
-      </x:c>
-      <x:c r="E5" s="9" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F5" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G5" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="9" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="I5" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J5" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="24" customHeight="1">
-      <x:c r="A6" s="9" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B6" s="9" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="9" t="str">
-        <x:v>boss_equipment</x:v>
-      </x:c>
-      <x:c r="D6" s="9" t="str">
-        <x:v>core_fragment,gate_sigil,court_medal</x:v>
-      </x:c>
-      <x:c r="E6" s="9" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F6" s="9" t="n">
+      <x:c r="G5" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G6" s="9" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H6" s="9" t="n">
+      <x:c r="H5" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I6" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J6" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K6" s="10" t="b">
+      <x:c r="I5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K5" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
